--- a/SPE-ING5 - Chronogramme.xlsx
+++ b/SPE-ING5 - Chronogramme.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Feuille 1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Feuille 1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>Communauté : Développement d'application web, mobile et UI/UX</t>
   </si>
@@ -90,7 +90,38 @@
   <si>
     <t>React.js, Nest.js, Keycloak, Golang
 Microservice, configuration Monorepo, NX
-CI/CD, Pipeline Github</t>
+CI/CD, Pipeline Github, Intégration IA, 
+"prompting engineering"</t>
+  </si>
+  <si>
+    <t>IDV-G4ME - Programmation en Unity</t>
+  </si>
+  <si>
+    <t>Unity, C#, scripting gameplay, physique, UI, architecture de scène, optimisation</t>
+  </si>
+  <si>
+    <t>IDV-MOB4</t>
+  </si>
+  <si>
+    <t>Swift, UIKit/SwiftUI, gestion tactile, dessin temps réel, logique interactive, UX mobile</t>
+  </si>
+  <si>
+    <t>IDV-AQL5 - Qualité du code</t>
+  </si>
+  <si>
+    <t>Golang, clean code, tests unitaires, analyse statique, gestion d’erreurs, modularité</t>
+  </si>
+  <si>
+    <t>IDV-CLO5 - Cloud</t>
+  </si>
+  <si>
+    <t>Cloud computing, Docker, déploiement, CI/CD, scalabilité, configuration environnement, réseau</t>
+  </si>
+  <si>
+    <t>SDC-2026 - ETNA Camp</t>
+  </si>
+  <si>
+    <t>Prototypage rapide, IA prédictive, modélisation, gestion données (éducation/diplômes), travail en équipe, priorisation, restitution technique</t>
   </si>
   <si>
     <r>
@@ -104,6 +135,7 @@
     <r>
       <rPr>
         <rFont val="Nunito Sans"/>
+        <b/>
         <i/>
         <color rgb="FFFFFFFF"/>
         <sz val="11.0"/>
@@ -123,12 +155,48 @@
     <t>FRESQ</t>
   </si>
   <si>
-    <t>Développement d’une plateforme pour le ministère de l’Enseignement supérieur – gestion des accréditations de diplômes (ESR)</t>
+    <r>
+      <rPr>
+        <rFont val="Nunito Sans"/>
+      </rPr>
+      <t xml:space="preserve">Développement d’une plateforme pour le ministère de l’Enseignement supérieur – gestion des accréditations de diplômes (MESR) : </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Nunito Sans"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://fresq.enseignementsup.gouv.fr/</t>
+    </r>
   </si>
   <si>
-    <t>Gestion de projet, DevOps, CI/CD, 
-tests automatisés, API REST, 
-Spring Boot, React, Git, UX.</t>
+    <t>Gestion de projet, architecture microservices, API REST, Java, Spring Boot (services Kinto), React, Git, CI/CD, DevOps, tests automatisés, UX, intégration systèmes métiers</t>
+  </si>
+  <si>
+    <t>Eureliens - CD28</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Nunito Sans"/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Développement du site internet officiel du département d'Eure et Loire : </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Nunito Sans"/>
+        <color rgb="FF1155CC"/>
+        <sz val="10.0"/>
+        <u/>
+      </rPr>
+      <t>https://eurelien.fr/</t>
+    </r>
+  </si>
+  <si>
+    <t>WordPress, PHP, Gutenberg, création de pages/templates, utilisation de composants existants, intégration UI, personnalisation thème, gestion des cookies (Tarte au Citron), environnement de production</t>
   </si>
   <si>
     <t>Travaux Personnels</t>
@@ -172,10 +240,98 @@
 hébergement sur VPS.</t>
   </si>
   <si>
+    <t>Language Go</t>
+  </si>
+  <si>
     <t>React moderne</t>
   </si>
   <si>
     <t>Architecture modulaire avec Vite, composants clairs et maintenables.</t>
+  </si>
+  <si>
+    <t>Vidéo youtube et documentaire tech</t>
+  </si>
+  <si>
+    <t>Chaine youtube underscore, Ici Amy Plant, Micode, V2F, Benjamin Code, Melvynx, EvoluNoob</t>
+  </si>
+  <si>
+    <t>Economie et business de la tech</t>
+  </si>
+  <si>
+    <t>Le Tech Show, Silicon Carne, Guillaume Moubeche</t>
+  </si>
+  <si>
+    <t>Mise en pratique hors ETNA</t>
+  </si>
+  <si>
+    <t>Site web pour une entreprise de 
+travaux sur cordes</t>
+  </si>
+  <si>
+    <t>Site vitrine responsive – Next.js / React – 
+UX métier – SEO local – Déploiement web</t>
+  </si>
+  <si>
+    <t>Projet en équipe Proximeet</t>
+  </si>
+  <si>
+    <t>Application mobile type réseau sociale
+ de proximité avec jeu, chat de conversation, 
+publications, stories, commentaires</t>
+  </si>
+  <si>
+    <t>Application web pour l'ETNA</t>
+  </si>
+  <si>
+    <t>Développement d'une application web complète pour la gestion avancé des classements des notes à l'ETNA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Nunito Sans"/>
+        <color rgb="FF000000"/>
+      </rPr>
+      <t xml:space="preserve">Micro-entreprise Webase : </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Nunito Sans"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>webase.fr</t>
+    </r>
+  </si>
+  <si>
+    <t>Lancement à côté de mes études et de mon alternance, une micro-entreprise proposant des services de developpement, maintenance d'application</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Nunito Sans"/>
+      </rPr>
+      <t xml:space="preserve">Site web pour une amie, portoflio complet pour sa candidature en Master : </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Nunito Sans"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>angeledelorme.fr</t>
+    </r>
+  </si>
+  <si>
+    <t>Conception de site vitrine, React.js, UI/UX design, intégration responsive, optimisation performance, gestion contenu, déploiement web, mise en valeur de profil professionnel</t>
+  </si>
+  <si>
+    <t>Site web pour un client dans mon auto-entreprise Webase, pour une entreprise de Géothermie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En cours </t>
+  </si>
+  <si>
+    <t>Évenements</t>
   </si>
   <si>
     <t>Evènements</t>
@@ -199,31 +355,33 @@
     <t>Apple WWDC 25</t>
   </si>
   <si>
-    <t>design Liquid Glass, iOS 26, macOS Tahoe, 
-Apple Intelligence, Xcode IA, 
-nouvelles UI gestuelles</t>
+    <t>Design Liquid Glass, iOS 26, macOS Tahoe, Apple Intelligence, Xcode IA, nouvelles UI gestuelles</t>
   </si>
   <si>
-    <t>Mise en pratique hors ETNA</t>
+    <t>Cursor Meetup Paris - March Edition</t>
   </si>
   <si>
-    <t>Site web pour une entreprise de 
-travaux sur cordes</t>
+    <t>Une soirée pour échanger des idées, nouer des contacts et découvrir comment cet outil révolutionne notre façon de construire.</t>
   </si>
   <si>
-    <t>Site vitrine responsive – Next.js / React – 
-UX métier – SEO local – Déploiement web</t>
+    <r>
+      <rPr>
+        <rFont val="Nunito Sans"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>Tekkit.io</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Nunito Sans"/>
+        <color rgb="FF000000"/>
+      </rPr>
+      <t xml:space="preserve"> - Evenement Tech &amp; IA</t>
+    </r>
   </si>
   <si>
-    <t>Projet en équipe Proximeet</t>
-  </si>
-  <si>
-    <t>Application mobile type réseau sociale
- de proximité avec jeu, chat de conversation, 
-publications, stories, commentaires</t>
-  </si>
-  <si>
-    <t>Évenements</t>
+    <t>Concourt Tekkit - Evenement et rencontre à Paris pour la remise des prix et participation aux rencontre candidats entreprise</t>
   </si>
 </sst>
 </file>
@@ -233,7 +391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="16">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -278,16 +436,42 @@
       <name val="Nunito Sans"/>
     </font>
     <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Nunito Sans"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Nunito Sans"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Nunito Sans"/>
+    </font>
+    <font>
       <color theme="0"/>
       <name val="Nunito Sans"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Nunito Sans"/>
+    </font>
+    <font>
+      <i/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Nunito Sans"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Nunito Sans"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,20 +522,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
+        <bgColor rgb="FFFFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor theme="7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE69138"/>
-        <bgColor rgb="FFE69138"/>
+        <fgColor rgb="FFE06666"/>
+        <bgColor rgb="FFE06666"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE06666"/>
-        <bgColor rgb="FFE06666"/>
+        <fgColor rgb="FFE69138"/>
+        <bgColor rgb="FFE69138"/>
       </patternFill>
     </fill>
   </fills>
@@ -402,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="41">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -435,6 +625,7 @@
     </xf>
     <xf borderId="0" fillId="7" fontId="6" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -444,36 +635,57 @@
     <xf borderId="0" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="9" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="10" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="11" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="0" fillId="12" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="12" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="9" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="10" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="11" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="12" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -484,6 +696,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -688,9 +904,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="30.75"/>
-    <col customWidth="1" min="3" max="3" width="36.38"/>
+    <col customWidth="1" min="1" max="1" width="18.38"/>
+    <col customWidth="1" min="2" max="2" width="34.0"/>
+    <col customWidth="1" min="3" max="3" width="40.88"/>
     <col customWidth="1" min="4" max="4" width="14.0"/>
     <col customWidth="1" min="5" max="5" width="18.13"/>
     <col customWidth="1" min="6" max="6" width="15.75"/>
@@ -954,7 +1170,7 @@
       <c r="Z7" s="13"/>
       <c r="AA7" s="13"/>
     </row>
-    <row r="8" ht="47.25" customHeight="1">
+    <row r="8" ht="45.75" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>12</v>
       </c>
@@ -986,7 +1202,7 @@
       <c r="Z8" s="13"/>
       <c r="AA8" s="13"/>
     </row>
-    <row r="9" ht="55.5" customHeight="1">
+    <row r="9" ht="60.0" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>14</v>
       </c>
@@ -998,80 +1214,79 @@
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
       <c r="Z9" s="13"/>
       <c r="AA9" s="13"/>
     </row>
-    <row r="10" ht="24.75" customHeight="1">
-      <c r="A10" s="14" t="s">
+    <row r="10" ht="47.25" customHeight="1">
+      <c r="A10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
-    </row>
-    <row r="11" ht="57.75" customHeight="1">
-      <c r="A11" s="16" t="s">
+      <c r="C10" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+    </row>
+    <row r="11" ht="36.75" customHeight="1">
+      <c r="A11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
       <c r="R11" s="13"/>
       <c r="S11" s="13"/>
       <c r="T11" s="13"/>
@@ -1083,76 +1298,75 @@
       <c r="Z11" s="13"/>
       <c r="AA11" s="13"/>
     </row>
-    <row r="12" ht="23.25" customHeight="1">
-      <c r="A12" s="6" t="s">
+    <row r="12" ht="39.75" customHeight="1">
+      <c r="A12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-    </row>
-    <row r="13" ht="34.5" customHeight="1">
-      <c r="A13" s="21" t="s">
+      <c r="C12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+    </row>
+    <row r="13" ht="33.75" customHeight="1">
+      <c r="A13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
       <c r="S13" s="13"/>
       <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" ht="30.75" customHeight="1">
-      <c r="B14" s="10" t="s">
+    <row r="14" ht="56.25" customHeight="1">
+      <c r="A14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="13"/>
@@ -1163,14 +1377,14 @@
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="13"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
       <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
+      <c r="S14" s="12"/>
       <c r="T14" s="13"/>
       <c r="U14" s="13"/>
       <c r="V14" s="13"/>
@@ -1180,175 +1394,176 @@
       <c r="Z14" s="13"/>
       <c r="AA14" s="13"/>
     </row>
-    <row r="15" ht="36.0" customHeight="1">
-      <c r="B15" s="10" t="s">
+    <row r="15" ht="24.75" customHeight="1">
+      <c r="A15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="16"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9"/>
+    </row>
+    <row r="16" ht="90.0" customHeight="1">
+      <c r="A16" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="13"/>
-    </row>
-    <row r="16" ht="36.0" customHeight="1">
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="13"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
       <c r="Z16" s="13"/>
       <c r="AA16" s="13"/>
     </row>
-    <row r="17" ht="32.25" customHeight="1">
-      <c r="B17" s="23" t="s">
+    <row r="17" ht="78.0" customHeight="1">
+      <c r="A17" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="B17" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="C17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="13"/>
-    </row>
-    <row r="18" ht="33.75" customHeight="1">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="25" t="s">
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="14"/>
+    </row>
+    <row r="18" ht="23.25" customHeight="1">
+      <c r="A18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
-      <c r="V18" s="26"/>
-      <c r="W18" s="26"/>
-      <c r="X18" s="26"/>
-      <c r="Y18" s="26"/>
-      <c r="Z18" s="26"/>
-      <c r="AA18" s="26"/>
-    </row>
-    <row r="19" ht="47.25" customHeight="1">
-      <c r="A19" s="28" t="s">
+      <c r="C18" s="23"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+    </row>
+    <row r="19" ht="36.0" customHeight="1">
+      <c r="A19" s="25" t="s">
         <v>34</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="27"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
       <c r="Z19" s="13"/>
       <c r="AA19" s="13"/>
     </row>
-    <row r="20" ht="35.25" customHeight="1">
+    <row r="20" ht="33.75" customHeight="1">
       <c r="B20" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="26" t="s">
         <v>38</v>
       </c>
       <c r="D20" s="13"/>
@@ -1357,13 +1572,13 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
-      <c r="J20" s="29"/>
+      <c r="J20" s="13"/>
       <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
       <c r="S20" s="13"/>
@@ -1376,57 +1591,53 @@
       <c r="Z20" s="13"/>
       <c r="AA20" s="13"/>
     </row>
-    <row r="21" ht="50.25" customHeight="1">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25" t="s">
+    <row r="21" ht="39.75" customHeight="1">
+      <c r="B21" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-      <c r="V21" s="26"/>
-      <c r="W21" s="26"/>
-      <c r="X21" s="26"/>
-      <c r="Y21" s="26"/>
-      <c r="Z21" s="26"/>
-      <c r="AA21" s="26"/>
-    </row>
-    <row r="22" ht="50.25" customHeight="1">
-      <c r="A22" s="31" t="s">
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13"/>
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+    </row>
+    <row r="22" ht="36.0" customHeight="1">
+      <c r="B22" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="C22" s="26" t="s">
         <v>42</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>43</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="13"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
@@ -1444,24 +1655,24 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" ht="51.75" customHeight="1">
-      <c r="B23" s="10" t="s">
+    <row r="23" ht="32.25" customHeight="1">
+      <c r="B23" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
@@ -1476,134 +1687,150 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="13"/>
     </row>
-    <row r="24" ht="24.75" customHeight="1">
-      <c r="A24" s="14" t="s">
+    <row r="24" ht="33.0" customHeight="1">
+      <c r="B24" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="13"/>
+    </row>
+    <row r="25" ht="33.0" customHeight="1">
+      <c r="B25" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
-      <c r="X24" s="20"/>
-      <c r="Y24" s="20"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
+      <c r="C25" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="13"/>
-      <c r="T25" s="13"/>
-      <c r="U25" s="13"/>
-      <c r="V25" s="13"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="27"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="27"/>
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="13"/>
       <c r="Z25" s="13"/>
       <c r="AA25" s="13"/>
     </row>
-    <row r="26">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
-      <c r="S26" s="13"/>
-      <c r="T26" s="13"/>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
+    <row r="26" ht="36.75" customHeight="1">
+      <c r="B26" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="27"/>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
       <c r="Y26" s="13"/>
       <c r="Z26" s="13"/>
       <c r="AA26" s="13"/>
     </row>
-    <row r="27">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="13"/>
-      <c r="U27" s="13"/>
-      <c r="V27" s="13"/>
+    <row r="27" ht="33.0" customHeight="1">
+      <c r="A27" s="28"/>
+      <c r="B27" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
       <c r="Z27" s="13"/>
       <c r="AA27" s="13"/>
     </row>
-    <row r="28">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
+    <row r="28" ht="42.75" customHeight="1">
+      <c r="A28" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>54</v>
+      </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
@@ -1622,21 +1849,24 @@
       <c r="Z28" s="13"/>
       <c r="AA28" s="13"/>
     </row>
-    <row r="29">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
+    <row r="29" ht="51.0" customHeight="1">
+      <c r="B29" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
       <c r="O29" s="13"/>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
@@ -1651,28 +1881,31 @@
       <c r="Z29" s="13"/>
       <c r="AA29" s="13"/>
     </row>
-    <row r="30">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="13"/>
-      <c r="R30" s="13"/>
-      <c r="S30" s="13"/>
-      <c r="T30" s="13"/>
-      <c r="U30" s="13"/>
+    <row r="30" ht="48.0" customHeight="1">
+      <c r="B30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
@@ -1680,57 +1913,63 @@
       <c r="Z30" s="13"/>
       <c r="AA30" s="13"/>
     </row>
-    <row r="31">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
+    <row r="31" ht="63.0" customHeight="1">
+      <c r="B31" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
       <c r="O31" s="13"/>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
       <c r="R31" s="13"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="13"/>
-      <c r="U31" s="13"/>
-      <c r="V31" s="13"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31" s="13"/>
       <c r="Z31" s="13"/>
       <c r="AA31" s="13"/>
     </row>
-    <row r="32">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
+    <row r="32" ht="67.5" customHeight="1">
+      <c r="B32" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="13"/>
-      <c r="U32" s="13"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
       <c r="V32" s="13"/>
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
@@ -1738,75 +1977,85 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
+    <row r="33" ht="51.75" customHeight="1">
+      <c r="B33" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
       <c r="R33" s="13"/>
       <c r="S33" s="13"/>
-      <c r="T33" s="13"/>
-      <c r="U33" s="13"/>
-      <c r="V33" s="13"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="30"/>
+      <c r="V33" s="30"/>
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
       <c r="Y33" s="13"/>
       <c r="Z33" s="13"/>
       <c r="AA33" s="13"/>
     </row>
-    <row r="34">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="13"/>
-      <c r="R34" s="13"/>
-      <c r="S34" s="13"/>
-      <c r="T34" s="13"/>
-      <c r="U34" s="13"/>
-      <c r="V34" s="13"/>
-      <c r="W34" s="13"/>
-      <c r="X34" s="13"/>
-      <c r="Y34" s="13"/>
-      <c r="Z34" s="13"/>
-      <c r="AA34" s="13"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
+    <row r="34" ht="24.75" customHeight="1">
+      <c r="A34" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
+      <c r="N34" s="24"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24"/>
+      <c r="Q34" s="24"/>
+      <c r="R34" s="24"/>
+      <c r="S34" s="24"/>
+      <c r="T34" s="24"/>
+      <c r="U34" s="24"/>
+      <c r="V34" s="24"/>
+      <c r="W34" s="24"/>
+      <c r="X34" s="24"/>
+      <c r="Y34" s="24"/>
+      <c r="Z34" s="24"/>
+      <c r="AA34" s="24"/>
+    </row>
+    <row r="35" ht="52.5" customHeight="1">
+      <c r="A35" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>68</v>
+      </c>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
+      <c r="J35" s="35"/>
       <c r="K35" s="13"/>
       <c r="L35" s="13"/>
       <c r="M35" s="13"/>
@@ -1825,17 +2074,20 @@
       <c r="Z35" s="13"/>
       <c r="AA35" s="13"/>
     </row>
-    <row r="36">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
+    <row r="36" ht="39.0" customHeight="1">
+      <c r="B36" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>70</v>
+      </c>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
+      <c r="J36" s="35"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
@@ -1854,10 +2106,13 @@
       <c r="Z36" s="13"/>
       <c r="AA36" s="13"/>
     </row>
-    <row r="37">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
+    <row r="37" ht="45.0" customHeight="1">
+      <c r="B37" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
@@ -1866,7 +2121,7 @@
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
+      <c r="L37" s="35"/>
       <c r="M37" s="13"/>
       <c r="N37" s="13"/>
       <c r="O37" s="13"/>
@@ -1883,10 +2138,13 @@
       <c r="Z37" s="13"/>
       <c r="AA37" s="13"/>
     </row>
-    <row r="38">
-      <c r="A38" s="13"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
+    <row r="38" ht="55.5" customHeight="1">
+      <c r="B38" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
@@ -1895,7 +2153,6 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
       <c r="M38" s="13"/>
       <c r="N38" s="13"/>
       <c r="O38" s="13"/>
@@ -1904,7 +2161,7 @@
       <c r="R38" s="13"/>
       <c r="S38" s="13"/>
       <c r="T38" s="13"/>
-      <c r="U38" s="13"/>
+      <c r="U38" s="35"/>
       <c r="V38" s="13"/>
       <c r="W38" s="13"/>
       <c r="X38" s="13"/>
@@ -1912,34 +2169,38 @@
       <c r="Z38" s="13"/>
       <c r="AA38" s="13"/>
     </row>
-    <row r="39">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13"/>
-      <c r="R39" s="13"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="13"/>
-      <c r="U39" s="13"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="13"/>
-      <c r="X39" s="13"/>
-      <c r="Y39" s="13"/>
-      <c r="Z39" s="13"/>
-      <c r="AA39" s="13"/>
+    <row r="39" ht="57.0" customHeight="1">
+      <c r="A39" s="28"/>
+      <c r="B39" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="39"/>
+      <c r="R39" s="39"/>
+      <c r="S39" s="39"/>
+      <c r="T39" s="39"/>
+      <c r="U39" s="40"/>
+      <c r="V39" s="39"/>
+      <c r="W39" s="39"/>
+      <c r="X39" s="39"/>
+      <c r="Y39" s="39"/>
+      <c r="Z39" s="39"/>
+      <c r="AA39" s="39"/>
     </row>
     <row r="40">
       <c r="A40" s="13"/>
@@ -30042,27 +30303,387 @@
       <c r="Z1008" s="13"/>
       <c r="AA1008" s="13"/>
     </row>
+    <row r="1009">
+      <c r="A1009" s="13"/>
+      <c r="B1009" s="13"/>
+      <c r="C1009" s="13"/>
+      <c r="D1009" s="13"/>
+      <c r="E1009" s="13"/>
+      <c r="F1009" s="13"/>
+      <c r="G1009" s="13"/>
+      <c r="H1009" s="13"/>
+      <c r="I1009" s="13"/>
+      <c r="J1009" s="13"/>
+      <c r="K1009" s="13"/>
+      <c r="L1009" s="13"/>
+      <c r="M1009" s="13"/>
+      <c r="N1009" s="13"/>
+      <c r="O1009" s="13"/>
+      <c r="P1009" s="13"/>
+      <c r="Q1009" s="13"/>
+      <c r="R1009" s="13"/>
+      <c r="S1009" s="13"/>
+      <c r="T1009" s="13"/>
+      <c r="U1009" s="13"/>
+      <c r="V1009" s="13"/>
+      <c r="W1009" s="13"/>
+      <c r="X1009" s="13"/>
+      <c r="Y1009" s="13"/>
+      <c r="Z1009" s="13"/>
+      <c r="AA1009" s="13"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="13"/>
+      <c r="B1010" s="13"/>
+      <c r="C1010" s="13"/>
+      <c r="D1010" s="13"/>
+      <c r="E1010" s="13"/>
+      <c r="F1010" s="13"/>
+      <c r="G1010" s="13"/>
+      <c r="H1010" s="13"/>
+      <c r="I1010" s="13"/>
+      <c r="J1010" s="13"/>
+      <c r="K1010" s="13"/>
+      <c r="L1010" s="13"/>
+      <c r="M1010" s="13"/>
+      <c r="N1010" s="13"/>
+      <c r="O1010" s="13"/>
+      <c r="P1010" s="13"/>
+      <c r="Q1010" s="13"/>
+      <c r="R1010" s="13"/>
+      <c r="S1010" s="13"/>
+      <c r="T1010" s="13"/>
+      <c r="U1010" s="13"/>
+      <c r="V1010" s="13"/>
+      <c r="W1010" s="13"/>
+      <c r="X1010" s="13"/>
+      <c r="Y1010" s="13"/>
+      <c r="Z1010" s="13"/>
+      <c r="AA1010" s="13"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="13"/>
+      <c r="B1011" s="13"/>
+      <c r="C1011" s="13"/>
+      <c r="D1011" s="13"/>
+      <c r="E1011" s="13"/>
+      <c r="F1011" s="13"/>
+      <c r="G1011" s="13"/>
+      <c r="H1011" s="13"/>
+      <c r="I1011" s="13"/>
+      <c r="J1011" s="13"/>
+      <c r="K1011" s="13"/>
+      <c r="L1011" s="13"/>
+      <c r="M1011" s="13"/>
+      <c r="N1011" s="13"/>
+      <c r="O1011" s="13"/>
+      <c r="P1011" s="13"/>
+      <c r="Q1011" s="13"/>
+      <c r="R1011" s="13"/>
+      <c r="S1011" s="13"/>
+      <c r="T1011" s="13"/>
+      <c r="U1011" s="13"/>
+      <c r="V1011" s="13"/>
+      <c r="W1011" s="13"/>
+      <c r="X1011" s="13"/>
+      <c r="Y1011" s="13"/>
+      <c r="Z1011" s="13"/>
+      <c r="AA1011" s="13"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="13"/>
+      <c r="B1012" s="13"/>
+      <c r="C1012" s="13"/>
+      <c r="D1012" s="13"/>
+      <c r="E1012" s="13"/>
+      <c r="F1012" s="13"/>
+      <c r="G1012" s="13"/>
+      <c r="H1012" s="13"/>
+      <c r="I1012" s="13"/>
+      <c r="J1012" s="13"/>
+      <c r="K1012" s="13"/>
+      <c r="L1012" s="13"/>
+      <c r="M1012" s="13"/>
+      <c r="N1012" s="13"/>
+      <c r="O1012" s="13"/>
+      <c r="P1012" s="13"/>
+      <c r="Q1012" s="13"/>
+      <c r="R1012" s="13"/>
+      <c r="S1012" s="13"/>
+      <c r="T1012" s="13"/>
+      <c r="U1012" s="13"/>
+      <c r="V1012" s="13"/>
+      <c r="W1012" s="13"/>
+      <c r="X1012" s="13"/>
+      <c r="Y1012" s="13"/>
+      <c r="Z1012" s="13"/>
+      <c r="AA1012" s="13"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="13"/>
+      <c r="B1013" s="13"/>
+      <c r="C1013" s="13"/>
+      <c r="D1013" s="13"/>
+      <c r="E1013" s="13"/>
+      <c r="F1013" s="13"/>
+      <c r="G1013" s="13"/>
+      <c r="H1013" s="13"/>
+      <c r="I1013" s="13"/>
+      <c r="J1013" s="13"/>
+      <c r="K1013" s="13"/>
+      <c r="L1013" s="13"/>
+      <c r="M1013" s="13"/>
+      <c r="N1013" s="13"/>
+      <c r="O1013" s="13"/>
+      <c r="P1013" s="13"/>
+      <c r="Q1013" s="13"/>
+      <c r="R1013" s="13"/>
+      <c r="S1013" s="13"/>
+      <c r="T1013" s="13"/>
+      <c r="U1013" s="13"/>
+      <c r="V1013" s="13"/>
+      <c r="W1013" s="13"/>
+      <c r="X1013" s="13"/>
+      <c r="Y1013" s="13"/>
+      <c r="Z1013" s="13"/>
+      <c r="AA1013" s="13"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="13"/>
+      <c r="B1014" s="13"/>
+      <c r="C1014" s="13"/>
+      <c r="D1014" s="13"/>
+      <c r="E1014" s="13"/>
+      <c r="F1014" s="13"/>
+      <c r="G1014" s="13"/>
+      <c r="H1014" s="13"/>
+      <c r="I1014" s="13"/>
+      <c r="J1014" s="13"/>
+      <c r="K1014" s="13"/>
+      <c r="L1014" s="13"/>
+      <c r="M1014" s="13"/>
+      <c r="N1014" s="13"/>
+      <c r="O1014" s="13"/>
+      <c r="P1014" s="13"/>
+      <c r="Q1014" s="13"/>
+      <c r="R1014" s="13"/>
+      <c r="S1014" s="13"/>
+      <c r="T1014" s="13"/>
+      <c r="U1014" s="13"/>
+      <c r="V1014" s="13"/>
+      <c r="W1014" s="13"/>
+      <c r="X1014" s="13"/>
+      <c r="Y1014" s="13"/>
+      <c r="Z1014" s="13"/>
+      <c r="AA1014" s="13"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="13"/>
+      <c r="B1015" s="13"/>
+      <c r="C1015" s="13"/>
+      <c r="D1015" s="13"/>
+      <c r="E1015" s="13"/>
+      <c r="F1015" s="13"/>
+      <c r="G1015" s="13"/>
+      <c r="H1015" s="13"/>
+      <c r="I1015" s="13"/>
+      <c r="J1015" s="13"/>
+      <c r="K1015" s="13"/>
+      <c r="L1015" s="13"/>
+      <c r="M1015" s="13"/>
+      <c r="N1015" s="13"/>
+      <c r="O1015" s="13"/>
+      <c r="P1015" s="13"/>
+      <c r="Q1015" s="13"/>
+      <c r="R1015" s="13"/>
+      <c r="S1015" s="13"/>
+      <c r="T1015" s="13"/>
+      <c r="U1015" s="13"/>
+      <c r="V1015" s="13"/>
+      <c r="W1015" s="13"/>
+      <c r="X1015" s="13"/>
+      <c r="Y1015" s="13"/>
+      <c r="Z1015" s="13"/>
+      <c r="AA1015" s="13"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="13"/>
+      <c r="B1016" s="13"/>
+      <c r="C1016" s="13"/>
+      <c r="D1016" s="13"/>
+      <c r="E1016" s="13"/>
+      <c r="F1016" s="13"/>
+      <c r="G1016" s="13"/>
+      <c r="H1016" s="13"/>
+      <c r="I1016" s="13"/>
+      <c r="J1016" s="13"/>
+      <c r="K1016" s="13"/>
+      <c r="L1016" s="13"/>
+      <c r="M1016" s="13"/>
+      <c r="N1016" s="13"/>
+      <c r="O1016" s="13"/>
+      <c r="P1016" s="13"/>
+      <c r="Q1016" s="13"/>
+      <c r="R1016" s="13"/>
+      <c r="S1016" s="13"/>
+      <c r="T1016" s="13"/>
+      <c r="U1016" s="13"/>
+      <c r="V1016" s="13"/>
+      <c r="W1016" s="13"/>
+      <c r="X1016" s="13"/>
+      <c r="Y1016" s="13"/>
+      <c r="Z1016" s="13"/>
+      <c r="AA1016" s="13"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="13"/>
+      <c r="B1017" s="13"/>
+      <c r="C1017" s="13"/>
+      <c r="D1017" s="13"/>
+      <c r="E1017" s="13"/>
+      <c r="F1017" s="13"/>
+      <c r="G1017" s="13"/>
+      <c r="H1017" s="13"/>
+      <c r="I1017" s="13"/>
+      <c r="J1017" s="13"/>
+      <c r="K1017" s="13"/>
+      <c r="L1017" s="13"/>
+      <c r="M1017" s="13"/>
+      <c r="N1017" s="13"/>
+      <c r="O1017" s="13"/>
+      <c r="P1017" s="13"/>
+      <c r="Q1017" s="13"/>
+      <c r="R1017" s="13"/>
+      <c r="S1017" s="13"/>
+      <c r="T1017" s="13"/>
+      <c r="U1017" s="13"/>
+      <c r="V1017" s="13"/>
+      <c r="W1017" s="13"/>
+      <c r="X1017" s="13"/>
+      <c r="Y1017" s="13"/>
+      <c r="Z1017" s="13"/>
+      <c r="AA1017" s="13"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="13"/>
+      <c r="B1018" s="13"/>
+      <c r="C1018" s="13"/>
+      <c r="D1018" s="13"/>
+      <c r="E1018" s="13"/>
+      <c r="F1018" s="13"/>
+      <c r="G1018" s="13"/>
+      <c r="H1018" s="13"/>
+      <c r="I1018" s="13"/>
+      <c r="J1018" s="13"/>
+      <c r="K1018" s="13"/>
+      <c r="L1018" s="13"/>
+      <c r="M1018" s="13"/>
+      <c r="N1018" s="13"/>
+      <c r="O1018" s="13"/>
+      <c r="P1018" s="13"/>
+      <c r="Q1018" s="13"/>
+      <c r="R1018" s="13"/>
+      <c r="S1018" s="13"/>
+      <c r="T1018" s="13"/>
+      <c r="U1018" s="13"/>
+      <c r="V1018" s="13"/>
+      <c r="W1018" s="13"/>
+      <c r="X1018" s="13"/>
+      <c r="Y1018" s="13"/>
+      <c r="Z1018" s="13"/>
+      <c r="AA1018" s="13"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="13"/>
+      <c r="B1019" s="13"/>
+      <c r="C1019" s="13"/>
+      <c r="D1019" s="13"/>
+      <c r="E1019" s="13"/>
+      <c r="F1019" s="13"/>
+      <c r="G1019" s="13"/>
+      <c r="H1019" s="13"/>
+      <c r="I1019" s="13"/>
+      <c r="J1019" s="13"/>
+      <c r="K1019" s="13"/>
+      <c r="L1019" s="13"/>
+      <c r="M1019" s="13"/>
+      <c r="N1019" s="13"/>
+      <c r="O1019" s="13"/>
+      <c r="P1019" s="13"/>
+      <c r="Q1019" s="13"/>
+      <c r="R1019" s="13"/>
+      <c r="S1019" s="13"/>
+      <c r="T1019" s="13"/>
+      <c r="U1019" s="13"/>
+      <c r="V1019" s="13"/>
+      <c r="W1019" s="13"/>
+      <c r="X1019" s="13"/>
+      <c r="Y1019" s="13"/>
+      <c r="Z1019" s="13"/>
+      <c r="AA1019" s="13"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="13"/>
+      <c r="B1020" s="13"/>
+      <c r="C1020" s="13"/>
+      <c r="D1020" s="13"/>
+      <c r="E1020" s="13"/>
+      <c r="F1020" s="13"/>
+      <c r="G1020" s="13"/>
+      <c r="H1020" s="13"/>
+      <c r="I1020" s="13"/>
+      <c r="J1020" s="13"/>
+      <c r="K1020" s="13"/>
+      <c r="L1020" s="13"/>
+      <c r="M1020" s="13"/>
+      <c r="N1020" s="13"/>
+      <c r="O1020" s="13"/>
+      <c r="P1020" s="13"/>
+      <c r="Q1020" s="13"/>
+      <c r="R1020" s="13"/>
+      <c r="S1020" s="13"/>
+      <c r="T1020" s="13"/>
+      <c r="U1020" s="13"/>
+      <c r="V1020" s="13"/>
+      <c r="W1020" s="13"/>
+      <c r="X1020" s="13"/>
+      <c r="Y1020" s="13"/>
+      <c r="Z1020" s="13"/>
+      <c r="AA1020" s="13"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="20">
+    <mergeCell ref="A1:AA1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:A27"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:A39"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="B16"/>
+    <hyperlink r:id="rId2" ref="B17"/>
+    <hyperlink r:id="rId3" ref="B31"/>
+    <hyperlink r:id="rId4" ref="B32"/>
+    <hyperlink r:id="rId5" ref="B39"/>
+  </hyperlinks>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>